--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.048,3 km</t>
+          <t>2.073,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.179 m</t>
+          <t>32.404 m</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -478,16 +478,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>888,9 km</t>
+          <t>904,0 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.359 m</t>
+          <t>9.497 m</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -518,16 +518,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>257,2 km</t>
+          <t>260,1 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.826 m</t>
+          <t>2.862 m</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>376,8 km</t>
+          <t>368,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.795 m</t>
+          <t>2.664 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>368,8 km</t>
+          <t>354,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.664 m</t>
+          <t>2.614 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.073,2 km</t>
+          <t>2.076,4 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.404 m</t>
+          <t>32.439 m</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.076,4 km</t>
+          <t>2.087,3 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.439 m</t>
+          <t>32.536 m</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.087,3 km</t>
+          <t>2.077,3 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.536 m</t>
+          <t>32.398 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.077,3 km</t>
+          <t>2.081,3 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.398 m</t>
+          <t>32.412 m</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.081,3 km</t>
+          <t>2.090,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.412 m</t>
+          <t>32.347 m</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,12 +498,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>354,8 km</t>
+          <t>357,5 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.614 m</t>
+          <t>2.574 m</t>
         </is>
       </c>
       <c r="D4" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.090,0 km</t>
+          <t>2.087,8 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.347 m</t>
+          <t>32.202 m</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.087,8 km</t>
+          <t>2.083,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.202 m</t>
+          <t>32.153 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -518,16 +518,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>260,1 km</t>
+          <t>262,5 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.862 m</t>
+          <t>2.871 m</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.083,7 km</t>
+          <t>2.073,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.153 m</t>
+          <t>32.005 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.073,7 km</t>
+          <t>2.081,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.005 m</t>
+          <t>32.088 m</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>357,5 km</t>
+          <t>339,2 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.574 m</t>
+          <t>2.561 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,80 +453,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marcos Felix</t>
+          <t>Fabio Oliveira</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.081,6 km</t>
+          <t>904,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.088 m</t>
+          <t>9.497 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>137</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fabio Oliveira</t>
+          <t>Cristiano Silva</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>904,0 km</t>
+          <t>339,2 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.497 m</t>
+          <t>2.561 m</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cristiano Silva</t>
+          <t>Juliana Nogueira</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>339,2 km</t>
+          <t>262,5 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.561 m</t>
+          <t>2.871 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Juliana Nogueira</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>262,5 km</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2.871 m</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
         <v>74</v>
       </c>
     </row>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,66 +450,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fabio Oliveira</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>904,0 km</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>9.497 m</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cristiano Silva</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>339,2 km</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2.561 m</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Juliana Nogueira</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>262,5 km</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2.871 m</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>74</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
